--- a/backend/storage/output/excel/train-no/Rail_Madad_Report_3_Top_20_Trains_13-07-2026.xlsx
+++ b/backend/storage/output/excel/train-no/Rail_Madad_Report_3_Top_20_Trains_13-07-2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,21 +32,13 @@
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <color rgb="00000000"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -67,7 +59,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -75,8 +67,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,27 +482,27 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>22503</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>CSMT-NGP SEWAGRAM EXP [SUPERFAST]</t>
+          <t>VIVEK EXPRESS [SUPERFAST]</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Central Railway</t>
+          <t>Northeast Frontier Railway</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>NAGPUR DIVISION</t>
+          <t>TINSUKIA DIVISION</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -524,27 +514,27 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>19414</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>KOAA - ADI EXPRESS [MAIL EXPRESS]</t>
+          <t>DADN-PRYJ EXP. [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Western Railway</t>
+          <t>North Central Railway</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AHMEDABAD DIVISION</t>
+          <t>PRAYAGRAJ DIVISION</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -556,7 +546,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>15910</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -576,7 +566,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -588,27 +578,27 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>12129</t>
+          <t>15228</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>PUNE HWH AZAD HIND EXP [SUPERFAST]</t>
+          <t>MFP-SMVB EXPRESS [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Central Railway</t>
+          <t>East Central Railway</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>PUNE DIVISION</t>
+          <t>SAMASTIPUR DIVISION</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -620,59 +610,59 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>HUMSAFAR EXPRESS [SUPERFAST]</t>
+          <t>HWH NDLS POORVA EXPRESS [SUPERFAST]</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>Eastern Railway</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>LUMDING DIVISION</t>
+          <t>HOWRAH DIVISION</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>12792</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>DNR-SC EXP [SUPERFAST]</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>South Central Railway</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>SECUNDERABAD DIVISION</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>39</t>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>11040</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>G-KOP MAHARASHTRA EXP [MAIL EXPRESS]</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Central Railway</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>PUNE DIVISION</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -684,27 +674,27 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>CSMT-G VIDARBHA EXP [SUPERFAST]</t>
+          <t>VIVEK EXPRESS [SUPERFAST]</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Central Railway</t>
+          <t>Northeast Frontier Railway</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>BOMBAY DIVISION</t>
+          <t>TINSUKIA DIVISION</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -716,27 +706,27 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>G-CSMT VIDARBHA EXP [SUPERFAST]</t>
+          <t>NZM-MAS GARIBRATH [GARIB RATH]</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Central Railway</t>
+          <t>Southern Railway</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>BOMBAY DIVISION</t>
+          <t>CHENNAI DIVISION</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -748,27 +738,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>02570</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>NDLS-DBG SPECIAL [TRAIN ON DEMAND]</t>
+          <t>CDG-DBRG EXPRESS [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>East Central Railway</t>
+          <t>Northeast Frontier Railway</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>SAMASTIPUR DIVISION</t>
+          <t>TINSUKIA DIVISION</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -780,27 +770,27 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>SHC GARIB RATH [GARIB RATH]</t>
+          <t>NGP-CSMT SEWAGRAM EXP. [SUPERFAST]</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Northern Railway</t>
+          <t>Central Railway</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>FIROZPUR DIVISION</t>
+          <t>NAGPUR DIVISION</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -812,27 +802,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>VIVEK EXPRESS [SUPERFAST]</t>
+          <t>GARIB RATH EX [GARIB RATH]</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>Northern Railway</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>TINSUKIA DIVISION</t>
+          <t>FIROZPUR DIVISION</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -844,27 +834,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>20808</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>HWH JAT HIMGIRI EXPRESS [MAIL EXPRESS]</t>
+          <t>ASR-VSKP SF HIRAKUD EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Eastern Railway</t>
+          <t>South Coast Railway</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>HOWRAH DIVISION</t>
+          <t>VISAKHAPATNAM DIVISION</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -876,27 +866,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>12296</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>AVADH ASSAM EXPRESS [MAIL EXPRESS]</t>
+          <t>DNR-SMVB SANGHAMITRA EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>South Western Railway</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>TINSUKIA DIVISION</t>
+          <t>BANGALORE DIVISION</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -908,27 +898,27 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>04013</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>LKQ-ANVT SPL [TRAIN ON DEMAND]</t>
+          <t>AVADH ASSAM EXPRESS [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Northern Railway</t>
+          <t>Northeast Frontier Railway</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>DELHI DIVISION</t>
+          <t>TINSUKIA DIVISION</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -940,27 +930,27 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>22533</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>OKHA-GHY DWARKA EXPRESS [MAIL EXPRESS]</t>
+          <t>GKP- YPR SF [SUPERFAST]</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>North Eastern Railway</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>LUMDING DIVISION</t>
+          <t>LUCKNOW DIVISION</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -972,27 +962,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>09189</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>MMCT-KIR SPECIAL [TRAIN ON DEMAND]</t>
+          <t>G-CSMT VIDARBHA EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Western Railway</t>
+          <t>Central Railway</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>MUMBAI DIVISION</t>
+          <t>BOMBAY DIVISION</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1014,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1036,27 +1026,27 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>12562</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>SWANTRATA SENANI EXPRESS [SUPERFAST]</t>
+          <t>KYQ-PURI EXPRESS [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>East Central Railway</t>
+          <t>Northeast Frontier Railway</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>SAMASTIPUR DIVISION</t>
+          <t>LUMDING DIVISION</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1068,27 +1058,27 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>ADI-HWH SUPERFAST EXPRESS [SUPERFAST]</t>
+          <t>BRAHMAPUTRA MAIL [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>South Eastern Railway</t>
+          <t>Northeast Frontier Railway</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>KHARAGPUR DIVISION</t>
+          <t>LUMDING DIVISION</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1100,27 +1090,27 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>01080</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>GKP-CSMT SPL [TRAIN ON DEMAND]</t>
+          <t>JBN-ED AMRIT BHARAT EXP [AMRIT BHARAT]</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Central Railway</t>
+          <t>Southern Railway</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>BOMBAY DIVISION</t>
+          <t>SALEM DIVISION</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
     </row>
